--- a/feedback_forms/006_educational_support_questionnaire--feedback_forms.xlsx
+++ b/feedback_forms/006_educational_support_questionnaire--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'instructor'}</t>
+          <t>instructor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Instructor'}</t>
+          <t>Instructor</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'tutor'}</t>
+          <t>tutor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Tutor'}</t>
+          <t>Tutor</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'math'}</t>
+          <t>math</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Math'}</t>
+          <t>Math</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'faculty'}</t>
+          <t>faculty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Faculty'}</t>
+          <t>Faculty</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'In person'}</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'funding'}</t>
+          <t>funding</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Funding'}</t>
+          <t>Funding</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Training'}</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'limited_training'}</t>
+          <t>limited_training</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Limited training'}</t>
+          <t>Limited training</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'limited_resources'}</t>
+          <t>limited_resources</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Limited resources'}</t>
+          <t>Limited resources</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'limited_support'}</t>
+          <t>limited_support</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Limited support'}</t>
+          <t>Limited support</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_time'}</t>
+          <t>lack_of_time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Lack of time'}</t>
+          <t>Lack of time</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'funding'}</t>
+          <t>funding</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Funding'}</t>
+          <t>Funding</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'equipment'}</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Equipment'}</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
